--- a/static/images/Leaderboard_Webpage.xlsx
+++ b/static/images/Leaderboard_Webpage.xlsx
@@ -1,108 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20361"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Nextcloud\Forschung\MedPrompting\Webseite\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6ADC91-71A2-4C51-9ABB-C777F6DF884B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10530" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>RQ1</t>
-  </si>
-  <si>
-    <t>RQ2 Number</t>
-  </si>
-  <si>
-    <t>RQ2 Letter</t>
-  </si>
-  <si>
-    <t>RQ2 Dot</t>
-  </si>
-  <si>
-    <t>AS Letter</t>
-  </si>
-  <si>
-    <t>AS Dot</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>GPT4o</t>
-  </si>
-  <si>
-    <t>Pixtral 12b</t>
-  </si>
-  <si>
-    <t>Gemma 3 12b</t>
-  </si>
-  <si>
-    <t>Llama 3.2 11b</t>
-  </si>
-  <si>
-    <t>JanusPro 7b</t>
-  </si>
-  <si>
-    <t>MedGemma 4b</t>
-  </si>
-  <si>
-    <t>AS Number</t>
-  </si>
-  <si>
-    <t>RQ3(2) Number</t>
-  </si>
-  <si>
-    <t>RQ3(2) Letter</t>
-  </si>
-  <si>
-    <t>RQ3(2) Dot</t>
-  </si>
-  <si>
-    <t>LLaVa Mistral 7b</t>
-  </si>
-  <si>
-    <t>LLaVa Vicuna 7b</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,24 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -477,357 +469,679 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="3" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" customWidth="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="13.7265625" customWidth="1" min="3" max="4"/>
+    <col width="12.26953125" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13.453125" customWidth="1" min="7" max="7"/>
+    <col width="13.6328125" customWidth="1" min="8" max="8"/>
+    <col width="10.90625" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RQ2 Number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RQ2 Letter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RQ2 Dot</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RQ3(2) Number</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RQ3(2) Letter</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RQ3(2) Dot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>AS Number</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>AS Letter</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>AS Dot</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GPT4o</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>50.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>59.3</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>59.7</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>51.6</v>
       </c>
-      <c r="F2">
-        <v>83.1</v>
-      </c>
-      <c r="G2">
-        <v>87.4</v>
-      </c>
-      <c r="H2">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="I2">
+      <c r="F2" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I2" t="n">
         <v>80</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>86</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>78.7</v>
       </c>
-      <c r="L2">
-        <v>70.599999999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
+      <c r="L2" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gemma 3 12b</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>50.9</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>57.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>58.5</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>55.6</v>
       </c>
-      <c r="F3">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="G3">
+      <c r="F3" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G3" t="n">
         <v>65.2</v>
       </c>
-      <c r="H3">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="I3">
+      <c r="H3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I3" t="n">
         <v>67.3</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>65.7</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>77</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>63.8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pixtral 12b</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>50.7</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>54.8</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>55.9</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>55.2</v>
       </c>
-      <c r="F4">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="G4">
+      <c r="F4" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G4" t="n">
         <v>72.8</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>76.2</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>69.7</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>76.3</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>87</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Llama 3.2 11b</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>49.3</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>50.3</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>50</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>53.9</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>52.1</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>52.5</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>55.5</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>49.3</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>50</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>55</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>51.8</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JanusPro 7b</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>49.2</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>49.6</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>49.7</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>50.6</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>48.9</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>49.8</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>67</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>47.3</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>52</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>68.3</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>53.2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LLaVa Mistral 7b</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>50.2</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>52.2</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>53.4</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>51.2</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>58</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>54</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>80.7</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>66.3</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>64.7</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>73.7</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>60.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LLaVa Vicuna 7b</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>49.9</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>50.8</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>49.9</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>51.3</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>56.6</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>50.7</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>70</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>65</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>57.7</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>75.7</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>57.8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MedGemma 4b</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>50.3</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>50.2</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>50.3</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>49.4</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>50.2</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>49.9</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>53.7</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>54.7</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>50</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>56</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>51.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Qwen 3.5 9b</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>90</v>
+      </c>
+      <c r="H10" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gemma 4 27b-a4b</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>91</v>
+      </c>
+      <c r="L11" t="n">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Qwen 3.5 9b (Reasoning Budget: 2048 Tokens)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>99</v>
+      </c>
+      <c r="J12" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Qwen 3.5 9b (Reasoning Budget: 4096 Tokens)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gemma 4 27b-a4b (Reasoning Budget: 2048 Tokens)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gemma 4 27b-a4b (Reasoning Budget: 4096 Tokens)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MedGemma 1.5 4b</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>54</v>
+      </c>
+      <c r="I16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>56</v>
+      </c>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="n">
+        <v>52.9</v>
       </c>
     </row>
   </sheetData>
